--- a/rules/CORE-000125/positive/01/data/unit-test-coreid-CG0390-positive.xlsx
+++ b/rules/CORE-000125/positive/01/data/unit-test-coreid-CG0390-positive.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ae.xpt" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Library" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ae.xpt" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -587,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:X7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -711,8 +711,6 @@
           <t>AEENTPT</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="n"/>
-      <c r="Z1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -835,8 +833,6 @@
           <t>End Reference Time Point</t>
         </is>
       </c>
-      <c r="Y2" s="4" t="n"/>
-      <c r="Z2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -959,8 +955,6 @@
           <t>Char</t>
         </is>
       </c>
-      <c r="Y3" s="4" t="n"/>
-      <c r="Z3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -1035,8 +1029,6 @@
       <c r="X4" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="Y4" s="4" t="n"/>
-      <c r="Z4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -1334,29 +1326,27 @@
           <t>N</t>
         </is>
       </c>
-      <c r="R7" s="7" t="n"/>
-      <c r="S7" s="7" t="n"/>
-      <c r="T7" s="6" t="inlineStr">
+      <c r="R7" s="7" t="inlineStr">
         <is>
           <t>TREATMENT</t>
         </is>
       </c>
-      <c r="U7" s="6" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>2013-08-30</t>
         </is>
       </c>
+      <c r="T7" s="6" t="n"/>
+      <c r="U7" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="V7" s="8" t="n"/>
-      <c r="W7" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="X7" s="8" t="n"/>
-      <c r="Y7" s="6" t="inlineStr">
+      <c r="W7" s="6" t="inlineStr">
         <is>
           <t>ONGOING</t>
         </is>
       </c>
-      <c r="Z7" s="6" t="inlineStr">
+      <c r="X7" s="8" t="inlineStr">
         <is>
           <t>2013-02-13</t>
         </is>
